--- a/output/pdf_financials_xlsx/JIVA.xlsx
+++ b/output/pdf_financials_xlsx/JIVA.xlsx
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>26.517059</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>25.322453</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>25.011067</v>
       </c>
     </row>
     <row r="93">
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.505402</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.019006</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.036249</v>
       </c>
     </row>
     <row r="104">
@@ -2116,10 +2116,10 @@
         <v>-0.059642</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>1.464083</v>
+        <v>1.483089</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.038516</v>
+        <v>-0.002267</v>
       </c>
     </row>
     <row r="107">
@@ -2797,7 +2797,11 @@
           <t>Prepaids and deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.055255</v>
       </c>
@@ -3456,7 +3460,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4090,7 +4098,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>26.517059</v>
       </c>
@@ -4685,7 +4697,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -5942,7 +5958,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>0.505402</v>
       </c>

--- a/output/pdf_financials_xlsx/JIVA.xlsx
+++ b/output/pdf_financials_xlsx/JIVA.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.159157</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.073937</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06827800000000001</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.159157</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.073937</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06827800000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.233518</v>
+        <v>0.074361</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.114785</v>
+        <v>0.040848</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.06827800000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/JIVA.xlsx
+++ b/output/pdf_financials_xlsx/JIVA.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>3.579857</v>
+        <v>0.6788380000000001</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.514529</v>
+        <v>0.091435</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.199824</v>
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-17.804799</v>
+        <v>-20.705818</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.788713</v>
+        <v>-3.211807</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.452157</v>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-133.8717663174833</v>
+        <v>-155.6841180126965</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-38.18760162384532</v>
+        <v>-43.98129395483787</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-9.827382839914272</v>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.6788380000000001</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.091435</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -6169,7 +6169,11 @@
           <t>Addition of intangible asset</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>-0.163766</v>
       </c>

--- a/output/pdf_financials_xlsx/JIVA.xlsx
+++ b/output/pdf_financials_xlsx/JIVA.xlsx
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>1.758906</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.447113</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.488141</v>
       </c>
     </row>
     <row r="68">
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.637426</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.155885</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.163861</v>
       </c>
     </row>
     <row r="71">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>7.712405</v>
+        <v>8.349831</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>6.164077</v>
+        <v>6.319962</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>6.456726</v>
+        <v>6.620587</v>
       </c>
     </row>
     <row r="72">
@@ -1706,13 +1706,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>-0.77972399265346</v>
+        <v>-0.8150131830808133</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>-0.5234819556776592</v>
+        <v>-0.5362920731435232</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>-0.5134245544220619</v>
+        <v>-0.5263696929186353</v>
       </c>
     </row>
     <row r="81">
@@ -3214,7 +3214,11 @@
           <t>Lease liabilities (Note 8)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -3910,7 +3914,11 @@
           <t>Lease liabilities (Note 9)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.637426</v>
       </c>
